--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120454617</v>
+        <v>120454618</v>
       </c>
       <c r="B2" t="n">
-        <v>91203</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525724</v>
+        <v>525708</v>
       </c>
       <c r="R2" t="n">
-        <v>6387271</v>
+        <v>6387276</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120454618</v>
+        <v>120454617</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>91203</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525708</v>
+        <v>525724</v>
       </c>
       <c r="R3" t="n">
-        <v>6387276</v>
+        <v>6387271</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -877,6 +877,1107 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124125613</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ödhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>525629</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6387175</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ingatorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124125017</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ödhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>525659</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6387072</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ingatorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124125619</v>
+      </c>
+      <c r="B6" t="n">
+        <v>105095</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ödhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>525629</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6387175</v>
+      </c>
+      <c r="S6" t="n">
+        <v>100</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ingatorp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124125728</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ödhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>525812</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6387227</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ingatorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124125691</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91010</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ödhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>525711</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6387268</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ingatorp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124125315</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ödhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>525471</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6387146</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ingatorp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124125235</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ödhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>525533</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6387109</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ingatorp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124124884</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ödhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>525669</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6387029</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ingatorp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124125616</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96332</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>53</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ödhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>525629</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6387175</v>
+      </c>
+      <c r="S12" t="n">
+        <v>100</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ingatorp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124125688</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ödhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>525711</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6387268</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ingatorp</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -990,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124125017</v>
+        <v>124125235</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>137</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1038,13 +1038,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525659</v>
+        <v>525533</v>
       </c>
       <c r="R5" t="n">
-        <v>6387072</v>
+        <v>6387109</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124125619</v>
+        <v>124125691</v>
       </c>
       <c r="B6" t="n">
-        <v>105095</v>
+        <v>91010</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,31 +1113,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1145,13 +1148,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525629</v>
+        <v>525711</v>
       </c>
       <c r="R6" t="n">
-        <v>6387175</v>
+        <v>6387268</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,7 +1211,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124125728</v>
+        <v>124125315</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1243,7 +1246,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1256,13 +1259,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525812</v>
+        <v>525471</v>
       </c>
       <c r="R7" t="n">
-        <v>6387227</v>
+        <v>6387146</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124125691</v>
+        <v>124125688</v>
       </c>
       <c r="B8" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,34 +1334,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>326</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1429,7 +1433,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124125315</v>
+        <v>124124884</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1464,7 +1468,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>108</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1477,13 +1481,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525471</v>
+        <v>525669</v>
       </c>
       <c r="R9" t="n">
-        <v>6387146</v>
+        <v>6387029</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1540,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124125235</v>
+        <v>124125616</v>
       </c>
       <c r="B10" t="n">
-        <v>98079</v>
+        <v>96332</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,32 +1556,28 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1588,13 +1588,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525533</v>
+        <v>525629</v>
       </c>
       <c r="R10" t="n">
-        <v>6387109</v>
+        <v>6387175</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124124884</v>
+        <v>124125619</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,32 +1663,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1699,13 +1695,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525669</v>
+        <v>525629</v>
       </c>
       <c r="R11" t="n">
-        <v>6387029</v>
+        <v>6387175</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1762,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124125616</v>
+        <v>124125728</v>
       </c>
       <c r="B12" t="n">
-        <v>96332</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1774,28 +1770,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1806,13 +1806,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525629</v>
+        <v>525812</v>
       </c>
       <c r="R12" t="n">
-        <v>6387175</v>
+        <v>6387227</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124125688</v>
+        <v>124125017</v>
       </c>
       <c r="B13" t="n">
         <v>98079</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525711</v>
+        <v>525659</v>
       </c>
       <c r="R13" t="n">
-        <v>6387268</v>
+        <v>6387072</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124125613</v>
+        <v>124125616</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,32 +891,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -1101,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124125616</v>
+        <v>124125688</v>
       </c>
       <c r="B6" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,28 +1109,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525629</v>
+        <v>525711</v>
       </c>
       <c r="R6" t="n">
-        <v>6387175</v>
+        <v>6387268</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124125619</v>
+        <v>124125017</v>
       </c>
       <c r="B7" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,28 +1220,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1252,13 +1256,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525629</v>
+        <v>525659</v>
       </c>
       <c r="R7" t="n">
-        <v>6387175</v>
+        <v>6387072</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124124884</v>
+        <v>124125619</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,32 +1331,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1363,13 +1363,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525669</v>
+        <v>525629</v>
       </c>
       <c r="R8" t="n">
-        <v>6387029</v>
+        <v>6387175</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124125017</v>
+        <v>124125691</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,35 +1438,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1474,13 +1473,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525659</v>
+        <v>525711</v>
       </c>
       <c r="R9" t="n">
-        <v>6387072</v>
+        <v>6387268</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1537,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124125688</v>
+        <v>124125235</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1572,7 +1571,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>137</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1585,13 +1584,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525711</v>
+        <v>525533</v>
       </c>
       <c r="R10" t="n">
-        <v>6387268</v>
+        <v>6387109</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1648,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124125691</v>
+        <v>124125613</v>
       </c>
       <c r="B11" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,34 +1659,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>291</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1695,13 +1695,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525711</v>
+        <v>525629</v>
       </c>
       <c r="R11" t="n">
-        <v>6387268</v>
+        <v>6387175</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124125235</v>
+        <v>124124884</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>108</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1806,13 +1806,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525533</v>
+        <v>525669</v>
       </c>
       <c r="R12" t="n">
-        <v>6387109</v>
+        <v>6387029</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124125616</v>
+        <v>124125688</v>
       </c>
       <c r="B4" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,28 +891,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -923,13 +927,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525629</v>
+        <v>525711</v>
       </c>
       <c r="R4" t="n">
-        <v>6387175</v>
+        <v>6387268</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124125315</v>
+        <v>124125728</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1021,7 +1025,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>134</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1034,13 +1038,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525471</v>
+        <v>525812</v>
       </c>
       <c r="R5" t="n">
-        <v>6387146</v>
+        <v>6387227</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,7 +1101,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124125688</v>
+        <v>124125017</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1132,7 +1136,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1145,13 +1149,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525711</v>
+        <v>525659</v>
       </c>
       <c r="R6" t="n">
-        <v>6387268</v>
+        <v>6387072</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,7 +1212,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124125017</v>
+        <v>124124884</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1243,7 +1247,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>108</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1256,13 +1260,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525659</v>
+        <v>525669</v>
       </c>
       <c r="R7" t="n">
-        <v>6387072</v>
+        <v>6387029</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1426,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124125691</v>
+        <v>124125613</v>
       </c>
       <c r="B9" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,34 +1442,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>291</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1473,13 +1478,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525711</v>
+        <v>525629</v>
       </c>
       <c r="R9" t="n">
-        <v>6387268</v>
+        <v>6387175</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1536,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124125235</v>
+        <v>124125691</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,35 +1553,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1584,13 +1588,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525533</v>
+        <v>525711</v>
       </c>
       <c r="R10" t="n">
-        <v>6387109</v>
+        <v>6387268</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1647,10 +1651,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124125613</v>
+        <v>124125616</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,32 +1663,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1758,7 +1758,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124124884</v>
+        <v>124125315</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1806,13 +1806,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525669</v>
+        <v>525471</v>
       </c>
       <c r="R12" t="n">
-        <v>6387029</v>
+        <v>6387146</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124125728</v>
+        <v>124125235</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>137</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525812</v>
+        <v>525533</v>
       </c>
       <c r="R13" t="n">
-        <v>6387227</v>
+        <v>6387109</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124125688</v>
+        <v>124125235</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -914,7 +914,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>137</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525711</v>
+        <v>525533</v>
       </c>
       <c r="R4" t="n">
-        <v>6387268</v>
+        <v>6387109</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124125728</v>
+        <v>124125613</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>291</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1038,13 +1038,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525812</v>
+        <v>525629</v>
       </c>
       <c r="R5" t="n">
-        <v>6387227</v>
+        <v>6387175</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124125017</v>
+        <v>124125619</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,32 +1113,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1149,13 +1145,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525659</v>
+        <v>525629</v>
       </c>
       <c r="R6" t="n">
-        <v>6387072</v>
+        <v>6387175</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,7 +1208,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124124884</v>
+        <v>124125688</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1247,7 +1243,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>326</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1260,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525669</v>
+        <v>525711</v>
       </c>
       <c r="R7" t="n">
-        <v>6387029</v>
+        <v>6387268</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1323,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124125619</v>
+        <v>124125017</v>
       </c>
       <c r="B8" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,28 +1331,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1367,13 +1367,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525629</v>
+        <v>525659</v>
       </c>
       <c r="R8" t="n">
-        <v>6387175</v>
+        <v>6387072</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124125613</v>
+        <v>124125691</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1442,35 +1442,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1478,13 +1477,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525629</v>
+        <v>525711</v>
       </c>
       <c r="R9" t="n">
-        <v>6387175</v>
+        <v>6387268</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1541,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124125691</v>
+        <v>124124884</v>
       </c>
       <c r="B10" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1553,34 +1552,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>108</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525711</v>
+        <v>525669</v>
       </c>
       <c r="R10" t="n">
-        <v>6387268</v>
+        <v>6387029</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124125616</v>
+        <v>124125728</v>
       </c>
       <c r="B11" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,28 +1663,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1695,13 +1699,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525629</v>
+        <v>525812</v>
       </c>
       <c r="R11" t="n">
-        <v>6387175</v>
+        <v>6387227</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1869,10 +1873,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124125235</v>
+        <v>124125616</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1881,32 +1885,28 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525533</v>
+        <v>525629</v>
       </c>
       <c r="R13" t="n">
-        <v>6387109</v>
+        <v>6387175</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -990,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124125613</v>
+        <v>124125315</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1038,13 +1038,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525629</v>
+        <v>525471</v>
       </c>
       <c r="R5" t="n">
-        <v>6387175</v>
+        <v>6387146</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124125619</v>
+        <v>124124884</v>
       </c>
       <c r="B6" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,28 +1113,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1145,13 +1149,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525629</v>
+        <v>525669</v>
       </c>
       <c r="R6" t="n">
-        <v>6387175</v>
+        <v>6387029</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,7 +1212,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124125688</v>
+        <v>124125728</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1243,7 +1247,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>134</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1256,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525711</v>
+        <v>525812</v>
       </c>
       <c r="R7" t="n">
-        <v>6387268</v>
+        <v>6387227</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1319,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124125017</v>
+        <v>124125616</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,32 +1335,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1367,13 +1367,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525659</v>
+        <v>525629</v>
       </c>
       <c r="R8" t="n">
-        <v>6387072</v>
+        <v>6387175</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124125691</v>
+        <v>124125619</v>
       </c>
       <c r="B9" t="n">
-        <v>91032</v>
+        <v>105117</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1442,34 +1442,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1477,13 +1474,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525711</v>
+        <v>525629</v>
       </c>
       <c r="R9" t="n">
-        <v>6387268</v>
+        <v>6387175</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1540,7 +1537,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124124884</v>
+        <v>124125613</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1575,7 +1572,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>291</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1588,13 +1585,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525669</v>
+        <v>525629</v>
       </c>
       <c r="R10" t="n">
-        <v>6387029</v>
+        <v>6387175</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1651,7 +1648,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124125728</v>
+        <v>124125017</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1686,7 +1683,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1699,13 +1696,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525812</v>
+        <v>525659</v>
       </c>
       <c r="R11" t="n">
-        <v>6387227</v>
+        <v>6387072</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1762,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124125315</v>
+        <v>124125691</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1774,35 +1771,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1810,13 +1806,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525471</v>
+        <v>525711</v>
       </c>
       <c r="R12" t="n">
-        <v>6387146</v>
+        <v>6387268</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1873,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124125616</v>
+        <v>124125688</v>
       </c>
       <c r="B13" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1885,28 +1881,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525629</v>
+        <v>525711</v>
       </c>
       <c r="R13" t="n">
-        <v>6387175</v>
+        <v>6387268</v>
       </c>
       <c r="S13" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124125017</v>
+        <v>124125691</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,35 +1660,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1696,13 +1695,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525659</v>
+        <v>525711</v>
       </c>
       <c r="R11" t="n">
-        <v>6387072</v>
+        <v>6387268</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1759,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124125691</v>
+        <v>124125017</v>
       </c>
       <c r="B12" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,34 +1770,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1806,13 +1806,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525711</v>
+        <v>525659</v>
       </c>
       <c r="R12" t="n">
-        <v>6387268</v>
+        <v>6387072</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124125235</v>
+        <v>124125691</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,35 +891,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -927,13 +926,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525533</v>
+        <v>525711</v>
       </c>
       <c r="R4" t="n">
-        <v>6387109</v>
+        <v>6387268</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124125315</v>
+        <v>124125619</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,32 +1001,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1038,13 +1033,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525471</v>
+        <v>525629</v>
       </c>
       <c r="R5" t="n">
-        <v>6387146</v>
+        <v>6387175</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1212,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124125728</v>
+        <v>124125616</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,32 +1219,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1260,13 +1251,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525812</v>
+        <v>525629</v>
       </c>
       <c r="R7" t="n">
-        <v>6387227</v>
+        <v>6387175</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124125616</v>
+        <v>124125613</v>
       </c>
       <c r="B8" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,28 +1326,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1430,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124125619</v>
+        <v>124125235</v>
       </c>
       <c r="B9" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1442,28 +1437,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -1474,13 +1473,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525629</v>
+        <v>525533</v>
       </c>
       <c r="R9" t="n">
-        <v>6387175</v>
+        <v>6387109</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1537,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124125613</v>
+        <v>124125688</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1572,7 +1571,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>326</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1585,13 +1584,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525629</v>
+        <v>525711</v>
       </c>
       <c r="R10" t="n">
-        <v>6387175</v>
+        <v>6387268</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1648,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124125691</v>
+        <v>124125315</v>
       </c>
       <c r="B11" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,34 +1659,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1695,13 +1695,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525711</v>
+        <v>525471</v>
       </c>
       <c r="R11" t="n">
-        <v>6387268</v>
+        <v>6387146</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124125688</v>
+        <v>124125728</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>134</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525711</v>
+        <v>525812</v>
       </c>
       <c r="R13" t="n">
-        <v>6387268</v>
+        <v>6387227</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124125691</v>
+        <v>124125017</v>
       </c>
       <c r="B4" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,34 +891,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -926,13 +927,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525711</v>
+        <v>525659</v>
       </c>
       <c r="R4" t="n">
-        <v>6387268</v>
+        <v>6387072</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124125619</v>
+        <v>124125691</v>
       </c>
       <c r="B5" t="n">
-        <v>105117</v>
+        <v>91032</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,31 +1002,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1033,13 +1037,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525629</v>
+        <v>525711</v>
       </c>
       <c r="R5" t="n">
-        <v>6387175</v>
+        <v>6387268</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1207,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124125616</v>
+        <v>124125315</v>
       </c>
       <c r="B7" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,28 +1223,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1251,13 +1259,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525629</v>
+        <v>525471</v>
       </c>
       <c r="R7" t="n">
-        <v>6387175</v>
+        <v>6387146</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124125613</v>
+        <v>124125619</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,32 +1334,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1425,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124125235</v>
+        <v>124125728</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1460,7 +1464,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>134</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1473,13 +1477,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525533</v>
+        <v>525812</v>
       </c>
       <c r="R9" t="n">
-        <v>6387109</v>
+        <v>6387227</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1536,7 +1540,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124125688</v>
+        <v>124125613</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1571,7 +1575,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>291</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1584,13 +1588,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525711</v>
+        <v>525629</v>
       </c>
       <c r="R10" t="n">
-        <v>6387268</v>
+        <v>6387175</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1647,10 +1651,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124125315</v>
+        <v>124125616</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,32 +1663,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1695,13 +1695,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525471</v>
+        <v>525629</v>
       </c>
       <c r="R11" t="n">
-        <v>6387146</v>
+        <v>6387175</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124125017</v>
+        <v>124125235</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>137</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1806,13 +1806,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525659</v>
+        <v>525533</v>
       </c>
       <c r="R12" t="n">
-        <v>6387072</v>
+        <v>6387109</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124125728</v>
+        <v>124125688</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>326</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525812</v>
+        <v>525711</v>
       </c>
       <c r="R13" t="n">
-        <v>6387227</v>
+        <v>6387268</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124125017</v>
+        <v>124125235</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -914,7 +914,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>137</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525659</v>
+        <v>525533</v>
       </c>
       <c r="R4" t="n">
-        <v>6387072</v>
+        <v>6387109</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124125691</v>
+        <v>124125728</v>
       </c>
       <c r="B5" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,34 +1002,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>134</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525711</v>
+        <v>525812</v>
       </c>
       <c r="R5" t="n">
-        <v>6387268</v>
+        <v>6387227</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1211,7 +1212,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124125315</v>
+        <v>124125017</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1246,7 +1247,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1259,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525471</v>
+        <v>525659</v>
       </c>
       <c r="R7" t="n">
-        <v>6387146</v>
+        <v>6387072</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124125619</v>
+        <v>124125688</v>
       </c>
       <c r="B8" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1334,28 +1335,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1366,13 +1371,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525629</v>
+        <v>525711</v>
       </c>
       <c r="R8" t="n">
-        <v>6387175</v>
+        <v>6387268</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124125728</v>
+        <v>124125616</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,32 +1446,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -1477,13 +1478,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525812</v>
+        <v>525629</v>
       </c>
       <c r="R9" t="n">
-        <v>6387227</v>
+        <v>6387175</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1651,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124125616</v>
+        <v>124125619</v>
       </c>
       <c r="B11" t="n">
-        <v>96354</v>
+        <v>105117</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,25 +1664,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1758,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124125235</v>
+        <v>124125691</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1770,35 +1771,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1806,13 +1806,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525533</v>
+        <v>525711</v>
       </c>
       <c r="R12" t="n">
-        <v>6387109</v>
+        <v>6387268</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124125688</v>
+        <v>124125315</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525711</v>
+        <v>525471</v>
       </c>
       <c r="R13" t="n">
-        <v>6387268</v>
+        <v>6387146</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124125235</v>
+        <v>124125315</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -914,7 +914,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525533</v>
+        <v>525471</v>
       </c>
       <c r="R4" t="n">
-        <v>6387109</v>
+        <v>6387146</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124125728</v>
+        <v>124125613</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>291</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1038,13 +1038,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525812</v>
+        <v>525629</v>
       </c>
       <c r="R5" t="n">
-        <v>6387227</v>
+        <v>6387175</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124124884</v>
+        <v>124125017</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1149,13 +1149,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525669</v>
+        <v>525659</v>
       </c>
       <c r="R6" t="n">
-        <v>6387029</v>
+        <v>6387072</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124125017</v>
+        <v>124125616</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,32 +1224,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1260,13 +1256,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525659</v>
+        <v>525629</v>
       </c>
       <c r="R7" t="n">
-        <v>6387072</v>
+        <v>6387175</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124125688</v>
+        <v>124125691</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,35 +1331,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1434,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124125616</v>
+        <v>124125235</v>
       </c>
       <c r="B9" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1446,28 +1441,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -1478,13 +1477,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525629</v>
+        <v>525533</v>
       </c>
       <c r="R9" t="n">
-        <v>6387175</v>
+        <v>6387109</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1541,7 +1540,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124125613</v>
+        <v>124125688</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1576,7 +1575,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>326</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1589,13 +1588,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525629</v>
+        <v>525711</v>
       </c>
       <c r="R10" t="n">
-        <v>6387175</v>
+        <v>6387268</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1652,10 +1651,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124125619</v>
+        <v>124125728</v>
       </c>
       <c r="B11" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1664,28 +1663,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1696,13 +1699,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525629</v>
+        <v>525812</v>
       </c>
       <c r="R11" t="n">
-        <v>6387175</v>
+        <v>6387227</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1759,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124125691</v>
+        <v>124125619</v>
       </c>
       <c r="B12" t="n">
-        <v>91032</v>
+        <v>105117</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,34 +1774,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1806,13 +1806,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525711</v>
+        <v>525629</v>
       </c>
       <c r="R12" t="n">
-        <v>6387268</v>
+        <v>6387175</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124125315</v>
+        <v>124124884</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>108</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525471</v>
+        <v>525669</v>
       </c>
       <c r="R13" t="n">
-        <v>6387146</v>
+        <v>6387029</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120454617</v>
+        <v>124125616</v>
       </c>
       <c r="B2" t="n">
-        <v>91293</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ingatorp, Sm</t>
+          <t>Ödhult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525724</v>
+        <v>525629</v>
       </c>
       <c r="R2" t="n">
-        <v>6387271</v>
+        <v>6387175</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,71 +758,74 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johannes Glännman</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johannes Glännman, Helena Uhlén</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120454618</v>
+        <v>124125691</v>
       </c>
       <c r="B3" t="n">
-        <v>98040</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ingatorp, Sm</t>
+          <t>Ödhult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525708</v>
+        <v>525711</v>
       </c>
       <c r="R3" t="n">
-        <v>6387276</v>
+        <v>6387268</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +849,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,76 +863,64 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johannes Glännman</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johannes Glännman, Helena Uhlén</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124125315</v>
+        <v>120454617</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ödhult, Sm</t>
+          <t>Ingatorp, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525471</v>
+        <v>525724</v>
       </c>
       <c r="R4" t="n">
-        <v>6387146</v>
+        <v>6387271</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +947,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,34 +961,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Johannes Glännman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Johannes Glännman, Helena Uhlén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124125613</v>
+        <v>120454618</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,28 +1007,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ödhult, Sm</t>
+          <t>Ingatorp, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525629</v>
+        <v>525708</v>
       </c>
       <c r="R5" t="n">
-        <v>6387175</v>
+        <v>6387276</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,12 +1044,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,34 +1058,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Johannes Glännman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Johannes Glännman, Helena Uhlén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124125017</v>
+        <v>124124884</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1136,7 +1106,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>108</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1149,13 +1119,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525659</v>
+        <v>525669</v>
       </c>
       <c r="R6" t="n">
-        <v>6387072</v>
+        <v>6387029</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,40 +1182,39 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124125616</v>
+        <v>124125017</v>
       </c>
       <c r="B7" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1256,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525629</v>
+        <v>525659</v>
       </c>
       <c r="R7" t="n">
-        <v>6387175</v>
+        <v>6387072</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,46 +1288,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124125691</v>
+        <v>124125235</v>
       </c>
       <c r="B8" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>137</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1366,13 +1331,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525711</v>
+        <v>525533</v>
       </c>
       <c r="R8" t="n">
-        <v>6387268</v>
+        <v>6387109</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,15 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124125235</v>
+        <v>124125315</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1424,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1477,13 +1437,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525533</v>
+        <v>525471</v>
       </c>
       <c r="R9" t="n">
-        <v>6387109</v>
+        <v>6387146</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1540,15 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124125688</v>
+        <v>124125613</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1530,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>291</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1588,13 +1543,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525711</v>
+        <v>525629</v>
       </c>
       <c r="R10" t="n">
-        <v>6387268</v>
+        <v>6387175</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1651,15 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124125728</v>
+        <v>124125688</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1686,7 +1636,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>326</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1699,10 +1649,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525812</v>
+        <v>525711</v>
       </c>
       <c r="R11" t="n">
-        <v>6387227</v>
+        <v>6387268</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1762,40 +1712,39 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124125619</v>
+        <v>124125728</v>
       </c>
       <c r="B12" t="n">
-        <v>105117</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1806,13 +1755,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525629</v>
+        <v>525812</v>
       </c>
       <c r="R12" t="n">
-        <v>6387175</v>
+        <v>6387227</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1869,44 +1818,35 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124124884</v>
+        <v>124125619</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1917,13 +1857,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525669</v>
+        <v>525629</v>
       </c>
       <c r="R13" t="n">
-        <v>6387029</v>
+        <v>6387175</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124125616</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124125691</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454617</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1073,6 +1093,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454618</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124124884</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1285,6 +1315,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124125017</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124125235</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1497,6 +1537,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124125315</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1603,6 +1648,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124125613</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1709,6 +1759,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124125688</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1811,6 +1866,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124125619</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1917,8 +1977,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124125728</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>